--- a/selenium-tests/UniHealthAI_Login_Test_Cases.xlsx
+++ b/selenium-tests/UniHealthAI_Login_Test_Cases.xlsx
@@ -60,7 +60,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>Passed</t>
   </si>
   <si>
     <t>TC-002</t>
